--- a/file/table/DAPC_LuminariasBogota.xlsx
+++ b/file/table/DAPC_LuminariasBogota.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2522759B-2FB0-493B-BF45-F0B3091F2084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCDA799-1866-4E3E-923E-37623432C0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28898" yWindow="6323" windowWidth="28996" windowHeight="15675" xr2:uid="{85940953-CB19-47BF-B353-0BB449A22871}"/>
   </bookViews>

--- a/file/table/DAPC_LuminariasBogota.xlsx
+++ b/file/table/DAPC_LuminariasBogota.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCDA799-1866-4E3E-923E-37623432C0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB384178-FFCE-44D7-BEA1-73CCD749568E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="6323" windowWidth="28996" windowHeight="15675" xr2:uid="{85940953-CB19-47BF-B353-0BB449A22871}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{85940953-CB19-47BF-B353-0BB449A22871}"/>
   </bookViews>
   <sheets>
     <sheet name="Luminaria" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <author>Test</author>
   </authors>
   <commentList>
-    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{4ABBA72E-6F12-4A80-B2BB-455BC2378CDA}">
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{4ABBA72E-6F12-4A80-B2BB-455BC2378CDA}">
       <text>
         <r>
           <rPr>
@@ -54,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C21" authorId="0" shapeId="0" xr:uid="{F6D654B6-8E83-4D4C-A5C6-AE230C9FA8C2}">
+    <comment ref="C22" authorId="0" shapeId="0" xr:uid="{F6D654B6-8E83-4D4C-A5C6-AE230C9FA8C2}">
       <text>
         <r>
           <rPr>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>LED</t>
   </si>
@@ -117,9 +117,6 @@
 (kWh-mes)</t>
   </si>
   <si>
-    <t>Estimación de consumo eléctrico de luminarias y costo de iluminación en Bogotá D.C.</t>
-  </si>
-  <si>
     <t>Consumo en GWh-mes</t>
   </si>
   <si>
@@ -138,9 +135,6 @@
     <t>Generación (MWh-mes)</t>
   </si>
   <si>
-    <t>Generación eléctrica requerida por tipo de tecnología</t>
-  </si>
-  <si>
     <t>Tipo de tecnología</t>
   </si>
   <si>
@@ -151,6 +145,21 @@
   </si>
   <si>
     <t>Termoeléctrica</t>
+  </si>
+  <si>
+    <t>1. Estimación de consumo eléctrico de luminarias y costo de iluminación en Bogotá D.C.</t>
+  </si>
+  <si>
+    <t>2. Generación eléctrica requerida por tipo de tecnología</t>
+  </si>
+  <si>
+    <t>Consumo</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Parámetro</t>
   </si>
 </sst>
 </file>
@@ -158,8 +167,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -209,7 +218,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -376,6 +385,96 @@
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -383,7 +482,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -394,31 +493,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -445,7 +529,7 @@
     <xf numFmtId="2" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -464,6 +548,27 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -801,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{319747BF-5D31-41A9-84AC-A476BC03E676}">
-  <dimension ref="B2:H23"/>
+  <dimension ref="B2:H24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
@@ -817,252 +922,268 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B4" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C4" s="23">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B4" s="9" t="s">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B5" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C5" s="23">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="33" x14ac:dyDescent="0.45">
-      <c r="B5" s="10" t="s">
+    <row r="6" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="B6" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C6" s="24">
         <v>650</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="33" x14ac:dyDescent="0.45">
-      <c r="B7" s="15" t="s">
+    <row r="8" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="B8" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D8" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F8" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H8" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B8" s="5" t="s">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B9" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C9" s="3">
         <v>159016</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D9" s="3">
         <v>40</v>
       </c>
-      <c r="E8" s="11">
-        <f>D8/1000</f>
+      <c r="E9" s="6">
+        <f>D9/1000</f>
         <v>0.04</v>
       </c>
-      <c r="F8" s="12">
-        <f>C8*E8*$C$3*$C$4</f>
+      <c r="F9" s="7">
+        <f>C9*E9*$C$4*$C$5</f>
         <v>1526553.6000000001</v>
       </c>
-      <c r="G8" s="12">
-        <f>F8*$C$5/1000000</f>
+      <c r="G9" s="7">
+        <f>F9*$C$6/1000000</f>
         <v>992.25984000000017</v>
       </c>
-      <c r="H8" s="13">
-        <f>(G8/$G$11)</f>
+      <c r="H9" s="8">
+        <f>(G9/$G$12)</f>
         <v>0.3641846677077713</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B9" s="5" t="s">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B10" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C10" s="3">
         <v>103644</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D10" s="3">
         <v>60</v>
       </c>
-      <c r="E9" s="11">
-        <f t="shared" ref="E9:E10" si="0">D9/1000</f>
+      <c r="E10" s="6">
+        <f t="shared" ref="E10:E11" si="0">D10/1000</f>
         <v>0.06</v>
       </c>
-      <c r="F9" s="12">
-        <f t="shared" ref="F9:F10" si="1">C9*E9*$C$3*$C$4</f>
+      <c r="F10" s="7">
+        <f t="shared" ref="F10:F11" si="1">C10*E10*$C$4*$C$5</f>
         <v>1492473.5999999999</v>
       </c>
-      <c r="G9" s="12">
-        <f t="shared" ref="G9:G10" si="2">F9*$C$5/1000000</f>
+      <c r="G10" s="7">
+        <f t="shared" ref="G10:G11" si="2">F10*$C$6/1000000</f>
         <v>970.1078399999999</v>
       </c>
-      <c r="H9" s="13">
-        <f>(G9/$G$11)</f>
+      <c r="H10" s="8">
+        <f>(G10/$G$12)</f>
         <v>0.35605431874689564</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B10" s="5" t="s">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C11" s="3">
         <v>88839</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D11" s="3">
         <v>55</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E11" s="6">
         <f t="shared" si="0"/>
         <v>5.5E-2</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F11" s="7">
         <f t="shared" si="1"/>
         <v>1172674.8</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G11" s="7">
         <f t="shared" si="2"/>
         <v>762.23861999999997</v>
       </c>
-      <c r="H10" s="13">
-        <f>(G10/$G$11)</f>
+      <c r="H11" s="8">
+        <f>(G11/$G$12)</f>
         <v>0.27976101354533311</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B11" s="18" t="s">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="19">
-        <f>SUM(C8:C10)</f>
+      <c r="C12" s="14">
+        <f>SUM(C9:C11)</f>
         <v>351499</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="21">
-        <f>SUM(F8:F10)</f>
+      <c r="D12" s="14"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="16">
+        <f>SUM(F9:F11)</f>
         <v>4191702</v>
       </c>
-      <c r="G11" s="21">
-        <f>SUM(G8:G10)</f>
+      <c r="G12" s="16">
+        <f>SUM(G9:G11)</f>
         <v>2724.6062999999999</v>
       </c>
-      <c r="H11" s="22">
-        <f>SUM(H8:H10)</f>
+      <c r="H12" s="17">
+        <f>SUM(H9:H11)</f>
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B14" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="18">
+        <f>F12/1000</f>
+        <v>4191.7020000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="19">
+        <f>F12/1000000</f>
+        <v>4.1917020000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="33" x14ac:dyDescent="0.45">
+      <c r="B19" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="3">
+        <v>700</v>
+      </c>
+      <c r="D20" s="18">
+        <f>ROUNDUP($C$16/C20,0)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="3">
+        <v>363</v>
+      </c>
+      <c r="D21" s="18">
+        <f>ROUNDUP($C$16/C21,0)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3">
+        <v>175</v>
+      </c>
+      <c r="D22" s="18">
+        <f>ROUNDUP($C$16/C22,0)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B23" s="21" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="2">
-        <f>F11/1000</f>
-        <v>4191.7020000000002</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="2">
-        <f>F11/1000000</f>
-        <v>4.1917020000000003</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="33" x14ac:dyDescent="0.45">
-      <c r="B18" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="3">
-        <v>700</v>
-      </c>
-      <c r="D19" s="23">
-        <f>ROUNDUP($C$15/C19,0)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="3">
-        <v>363</v>
-      </c>
-      <c r="D20" s="23">
-        <f>ROUNDUP($C$15/C20,0)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="3">
-        <v>175</v>
-      </c>
-      <c r="D21" s="23">
-        <f>ROUNDUP($C$15/C21,0)</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B22" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="27">
+      <c r="C23" s="22">
         <f>8500000/12</f>
         <v>708333.33333333337</v>
       </c>
-      <c r="D22" s="23">
-        <f>$C$15/C22</f>
+      <c r="D23" s="18">
+        <f>$C$16/C23</f>
         <v>5.9176969411764702E-3</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B23" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B24" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="20">
         <v>150</v>
       </c>
-      <c r="D23" s="24">
-        <f>ROUNDUP($C$15/C23,0)</f>
+      <c r="D24" s="19">
+        <f>ROUNDUP($C$16/C24,0)</f>
         <v>28</v>
       </c>
     </row>

--- a/file/table/DAPC_LuminariasBogota.xlsx
+++ b/file/table/DAPC_LuminariasBogota.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB384178-FFCE-44D7-BEA1-73CCD749568E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0AE588-6C63-4D5B-991F-7DEC5178EEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{85940953-CB19-47BF-B353-0BB449A22871}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{85940953-CB19-47BF-B353-0BB449A22871}"/>
   </bookViews>
   <sheets>
     <sheet name="Luminaria" sheetId="1" r:id="rId1"/>
@@ -907,25 +907,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{319747BF-5D31-41A9-84AC-A476BC03E676}">
   <dimension ref="B2:H24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.19921875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.86328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.53125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.1328125" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.06640625" style="1"/>
+    <col min="8" max="8" width="13.109375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="25" t="s">
         <v>28</v>
       </c>
@@ -933,7 +933,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="27" t="s">
         <v>7</v>
       </c>
@@ -941,7 +941,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="27" t="s">
         <v>11</v>
       </c>
@@ -949,7 +949,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B6" s="28" t="s">
         <v>8</v>
       </c>
@@ -957,7 +957,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
         <v>3</v>
       </c>
@@ -980,12 +980,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>0</v>
       </c>
       <c r="C9" s="3">
-        <v>159016</v>
+        <v>59016</v>
       </c>
       <c r="D9" s="3">
         <v>40</v>
@@ -996,23 +996,23 @@
       </c>
       <c r="F9" s="7">
         <f>C9*E9*$C$4*$C$5</f>
-        <v>1526553.6000000001</v>
+        <v>566553.59999999998</v>
       </c>
       <c r="G9" s="7">
         <f>F9*$C$6/1000000</f>
-        <v>992.25984000000017</v>
+        <v>368.25984</v>
       </c>
       <c r="H9" s="8">
         <f>(G9/$G$12)</f>
-        <v>0.3641846677077713</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.45">
+        <v>0.31620972684073584</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="3">
-        <v>103644</v>
+        <v>3644</v>
       </c>
       <c r="D10" s="3">
         <v>60</v>
@@ -1023,18 +1023,18 @@
       </c>
       <c r="F10" s="7">
         <f t="shared" ref="F10:F11" si="1">C10*E10*$C$4*$C$5</f>
-        <v>1492473.5999999999</v>
+        <v>52473.599999999999</v>
       </c>
       <c r="G10" s="7">
         <f t="shared" ref="G10:G11" si="2">F10*$C$6/1000000</f>
-        <v>970.1078399999999</v>
+        <v>34.107840000000003</v>
       </c>
       <c r="H10" s="8">
         <f>(G10/$G$12)</f>
-        <v>0.35605431874689564</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.45">
+        <v>2.9287013130531756E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>2</v>
       </c>
@@ -1058,38 +1058,38 @@
       </c>
       <c r="H11" s="8">
         <f>(G11/$G$12)</f>
-        <v>0.27976101354533311</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.45">
+        <v>0.65450326002873249</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="14">
         <f>SUM(C9:C11)</f>
-        <v>351499</v>
+        <v>151499</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="15"/>
       <c r="F12" s="16">
         <f>SUM(F9:F11)</f>
-        <v>4191702</v>
+        <v>1791702</v>
       </c>
       <c r="G12" s="16">
         <f>SUM(G9:G11)</f>
-        <v>2724.6062999999999</v>
+        <v>1164.6062999999999</v>
       </c>
       <c r="H12" s="17">
         <f>SUM(H9:H11)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
         <v>26</v>
       </c>
@@ -1097,25 +1097,25 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="18">
         <f>F12/1000</f>
-        <v>4191.7020000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
+        <v>1791.702</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="19">
         <f>F12/1000000</f>
-        <v>4.1917020000000003</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" ht="33" x14ac:dyDescent="0.45">
+        <v>1.7917019999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
         <v>20</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>15</v>
       </c>
@@ -1135,10 +1135,10 @@
       </c>
       <c r="D20" s="18">
         <f>ROUNDUP($C$16/C20,0)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -1147,10 +1147,10 @@
       </c>
       <c r="D21" s="18">
         <f>ROUNDUP($C$16/C21,0)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -1159,10 +1159,10 @@
       </c>
       <c r="D22" s="18">
         <f>ROUNDUP($C$16/C22,0)</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" s="21" t="s">
         <v>21</v>
       </c>
@@ -1172,10 +1172,10 @@
       </c>
       <c r="D23" s="18">
         <f>$C$16/C23</f>
-        <v>5.9176969411764702E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
+        <v>2.5294616470588234E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" s="9" t="s">
         <v>23</v>
       </c>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D24" s="19">
         <f>ROUNDUP($C$16/C24,0)</f>
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/file/table/DAPC_LuminariasBogota.xlsx
+++ b/file/table/DAPC_LuminariasBogota.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29908"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0AE588-6C63-4D5B-991F-7DEC5178EEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20797EA5-5041-4B02-A0AC-28ACF181706A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{85940953-CB19-47BF-B353-0BB449A22871}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{85940953-CB19-47BF-B353-0BB449A22871}"/>
   </bookViews>
   <sheets>
     <sheet name="Luminaria" sheetId="1" r:id="rId1"/>
@@ -104,9 +104,6 @@
     <t>Potencia (kWatt)</t>
   </si>
   <si>
-    <t>Costo anual en millones de $</t>
-  </si>
-  <si>
     <t>Dias promedio por mes</t>
   </si>
   <si>
@@ -160,6 +157,9 @@
   </si>
   <si>
     <t>Parámetro</t>
+  </si>
+  <si>
+    <t>Costo mensual en millones de $</t>
   </si>
 </sst>
 </file>
@@ -562,10 +562,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -907,33 +907,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{319747BF-5D31-41A9-84AC-A476BC03E676}">
   <dimension ref="B2:H24"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.88671875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.53125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.19921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.86328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.53125" style="2" customWidth="1"/>
     <col min="7" max="7" width="14.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="1"/>
+    <col min="8" max="8" width="13.1328125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B3" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B4" s="27" t="s">
         <v>7</v>
       </c>
@@ -941,15 +941,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B5" s="27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="23">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="33" x14ac:dyDescent="0.45">
       <c r="B6" s="28" t="s">
         <v>8</v>
       </c>
@@ -957,7 +957,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="33" x14ac:dyDescent="0.45">
       <c r="B8" s="10" t="s">
         <v>3</v>
       </c>
@@ -971,16 +971,16 @@
         <v>9</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B9" s="4" t="s">
         <v>0</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>0.31620972684073584</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B10" s="4" t="s">
         <v>1</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>2.9287013130531756E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B11" s="4" t="s">
         <v>2</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>0.65450326002873249</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B12" s="13" t="s">
         <v>4</v>
       </c>
@@ -1084,51 +1084,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B14" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B15" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B16" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" s="18">
         <f>F12/1000</f>
         <v>1791.702</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B17" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="19">
         <f>F12/1000000</f>
         <v>1.7917019999999999</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="33.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4" ht="33" x14ac:dyDescent="0.45">
       <c r="B19" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B20" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="3">
         <v>700</v>
@@ -1138,9 +1138,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B21" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" s="3">
         <v>363</v>
@@ -1150,9 +1150,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B22" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="3">
         <v>175</v>
@@ -1162,9 +1162,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B23" s="21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C23" s="22">
         <f>8500000/12</f>
@@ -1175,9 +1175,9 @@
         <v>2.5294616470588234E-3</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B24" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" s="20">
         <v>150</v>
